--- a/sorties/classement_marques_complet.xlsx
+++ b/sorties/classement_marques_complet.xlsx
@@ -11,7 +11,7 @@
     <sheet name="lecture" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'classement'!$A$1:$K$399</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'classement'!$A$1:$L$399</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K399"/>
+  <dimension ref="A1:L399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -436,6 +436,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,6 +495,11 @@
           <t>gamme_halal</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>profil</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +541,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -576,6 +587,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -617,6 +633,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -658,6 +679,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -699,6 +725,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -740,6 +771,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -781,6 +817,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -822,6 +863,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -863,6 +909,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -904,6 +955,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -945,6 +1001,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -986,6 +1047,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1027,6 +1093,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1068,6 +1139,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1109,6 +1185,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1150,6 +1231,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1191,6 +1277,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1232,6 +1323,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1273,6 +1369,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1314,6 +1415,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1355,6 +1461,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1396,6 +1507,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1437,6 +1553,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1478,6 +1599,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1519,6 +1645,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1560,6 +1691,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1601,6 +1737,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1642,6 +1783,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1683,6 +1829,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1724,6 +1875,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1765,6 +1921,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1806,6 +1967,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1847,6 +2013,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1888,6 +2059,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1929,6 +2105,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1970,6 +2151,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2011,6 +2197,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2052,6 +2243,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2093,6 +2289,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2134,6 +2335,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2175,6 +2381,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2216,6 +2427,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2257,6 +2473,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2298,6 +2519,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2339,6 +2565,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2380,6 +2611,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2421,6 +2657,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2462,6 +2703,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2503,6 +2749,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2544,6 +2795,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2585,6 +2841,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2626,6 +2887,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2667,6 +2933,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2708,6 +2979,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2749,6 +3025,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2790,6 +3071,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2831,6 +3117,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2872,6 +3163,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2913,6 +3209,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2954,6 +3255,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2995,6 +3301,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3036,6 +3347,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3077,6 +3393,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3118,6 +3439,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3159,6 +3485,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3200,6 +3531,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3241,6 +3577,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3282,6 +3623,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3323,6 +3669,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3364,6 +3715,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3405,6 +3761,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3446,6 +3807,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3487,6 +3853,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3528,6 +3899,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3569,6 +3945,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3610,6 +3991,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3651,6 +4037,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3692,6 +4083,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3733,6 +4129,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3774,6 +4175,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3815,6 +4221,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3856,6 +4267,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3897,6 +4313,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3938,6 +4359,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3979,6 +4405,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4020,6 +4451,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4061,6 +4497,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4102,6 +4543,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4143,6 +4589,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4184,6 +4635,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4225,6 +4681,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4266,6 +4727,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4307,6 +4773,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4348,6 +4819,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4389,6 +4865,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4430,6 +4911,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4471,6 +4957,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4512,6 +5003,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4553,6 +5049,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4594,6 +5095,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4635,6 +5141,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4676,6 +5187,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4717,6 +5233,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4758,6 +5279,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4799,6 +5325,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4840,6 +5371,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4881,6 +5417,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4922,6 +5463,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4963,6 +5509,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5004,6 +5555,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5045,6 +5601,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5086,6 +5647,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5127,6 +5693,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5168,6 +5739,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5209,6 +5785,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5250,6 +5831,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5291,6 +5877,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5332,6 +5923,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5373,6 +5969,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5414,6 +6015,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5455,6 +6061,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5496,6 +6107,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5537,6 +6153,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5578,6 +6199,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5619,6 +6245,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5660,6 +6291,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5701,6 +6337,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5742,6 +6383,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5783,6 +6429,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5824,6 +6475,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5865,6 +6521,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5906,6 +6567,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5947,6 +6613,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5988,6 +6659,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6029,6 +6705,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6070,6 +6751,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6111,6 +6797,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6152,6 +6843,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6193,6 +6889,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6234,6 +6935,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6275,6 +6981,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6316,6 +7027,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6357,6 +7073,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6398,6 +7119,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6439,6 +7165,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6480,6 +7211,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6521,6 +7257,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6562,6 +7303,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6603,6 +7349,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6644,6 +7395,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6685,6 +7441,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -6726,6 +7487,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6767,6 +7533,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6808,6 +7579,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -6849,6 +7625,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6890,6 +7671,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6931,6 +7717,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -6972,6 +7763,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7013,6 +7809,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -7054,6 +7855,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -7095,6 +7901,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7136,6 +7947,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7177,6 +7993,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7218,6 +8039,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7259,6 +8085,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7300,6 +8131,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7341,6 +8177,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7382,6 +8223,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7423,6 +8269,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7464,6 +8315,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7505,6 +8361,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7546,6 +8407,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -7587,6 +8453,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -7628,6 +8499,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -7669,6 +8545,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -7710,6 +8591,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -7751,6 +8637,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -7792,6 +8683,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -7833,6 +8729,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -7874,6 +8775,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -7915,6 +8821,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -7956,6 +8867,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -7997,6 +8913,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -8038,6 +8959,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -8079,6 +9005,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -8120,6 +9051,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -8161,6 +9097,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -8202,6 +9143,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -8243,6 +9189,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -8284,6 +9235,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -8325,6 +9281,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -8366,6 +9327,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8407,6 +9373,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -8448,6 +9419,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -8489,6 +9465,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -8530,6 +9511,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -8571,6 +9557,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -8612,6 +9603,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -8653,6 +9649,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -8694,6 +9695,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -8735,6 +9741,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -8776,6 +9787,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -8817,6 +9833,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -8858,6 +9879,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -8899,6 +9925,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -8940,6 +9971,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -8981,6 +10017,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -9022,6 +10063,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -9063,6 +10109,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -9104,6 +10155,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -9145,6 +10201,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -9186,6 +10247,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -9227,6 +10293,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -9268,6 +10339,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -9309,6 +10385,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -9350,6 +10431,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -9391,6 +10477,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -9432,6 +10523,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -9473,6 +10569,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -9514,6 +10615,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -9555,6 +10661,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -9596,6 +10707,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -9637,6 +10753,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -9678,6 +10799,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -9719,6 +10845,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -9760,6 +10891,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -9801,6 +10937,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -9842,6 +10983,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -9883,6 +11029,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -9924,6 +11075,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -9965,6 +11121,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -10006,6 +11167,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10047,6 +11213,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -10088,6 +11259,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -10129,6 +11305,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -10170,6 +11351,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -10211,6 +11397,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -10252,6 +11443,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -10293,6 +11489,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -10334,6 +11535,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -10375,6 +11581,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -10416,6 +11627,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -10457,6 +11673,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -10498,6 +11719,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -10539,6 +11765,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -10580,6 +11811,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -10621,6 +11857,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -10662,6 +11903,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -10703,6 +11949,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -10744,6 +11995,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -10785,6 +12041,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -10826,6 +12087,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -10867,6 +12133,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -10908,6 +12179,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -10949,6 +12225,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -10990,6 +12271,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -11031,6 +12317,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -11072,6 +12363,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -11113,6 +12409,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -11154,6 +12455,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -11195,6 +12501,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -11236,6 +12547,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -11277,6 +12593,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -11318,6 +12639,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -11359,6 +12685,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -11400,6 +12731,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -11441,6 +12777,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -11482,6 +12823,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -11523,6 +12869,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -11564,6 +12915,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -11605,6 +12961,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -11646,6 +13007,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -11687,6 +13053,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -11728,6 +13099,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -11769,6 +13145,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -11810,6 +13191,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -11851,6 +13237,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -11892,6 +13283,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -11933,6 +13329,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -11974,6 +13375,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -12015,6 +13421,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -12056,6 +13467,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -12097,6 +13513,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -12138,6 +13559,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>gamme halal marginale (&lt; 5 produits)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -12179,6 +13605,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -12220,6 +13651,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -12261,6 +13697,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -12302,6 +13743,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -12343,6 +13789,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -12384,6 +13835,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -12425,6 +13881,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -12466,6 +13927,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -12507,6 +13973,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -12548,6 +14019,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -12589,6 +14065,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -12630,6 +14111,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -12671,6 +14157,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -12712,6 +14203,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -12753,6 +14249,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -12794,6 +14295,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -12835,6 +14341,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -12876,6 +14387,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -12917,6 +14433,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -12958,6 +14479,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -12999,6 +14525,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -13040,6 +14571,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -13081,6 +14617,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -13122,6 +14663,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -13163,6 +14709,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -13204,6 +14755,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -13245,6 +14801,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -13286,6 +14847,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -13327,6 +14893,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -13368,6 +14939,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -13409,6 +14985,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -13450,6 +15031,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -13491,6 +15077,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -13532,6 +15123,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -13573,6 +15169,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -13614,6 +15215,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -13655,6 +15261,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -13696,6 +15307,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -13737,6 +15353,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -13778,6 +15399,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -13819,6 +15445,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -13860,6 +15491,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -13901,6 +15537,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -13942,6 +15583,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -13983,6 +15629,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -14024,6 +15675,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -14065,6 +15721,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -14106,6 +15767,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -14147,6 +15813,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -14188,6 +15859,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -14229,6 +15905,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -14270,6 +15951,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -14311,6 +15997,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -14352,6 +16043,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -14393,6 +16089,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -14434,6 +16135,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -14475,6 +16181,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -14516,6 +16227,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -14557,6 +16273,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -14598,6 +16319,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -14639,6 +16365,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -14680,6 +16411,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -14721,6 +16457,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -14762,6 +16503,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -14803,6 +16549,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -14844,6 +16595,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -14885,6 +16641,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -14926,6 +16687,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -14967,6 +16733,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -15008,6 +16779,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -15049,6 +16825,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -15090,6 +16871,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -15131,6 +16917,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -15172,6 +16963,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -15213,6 +17009,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -15254,6 +17055,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -15295,6 +17101,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -15336,6 +17147,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -15377,6 +17193,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -15418,6 +17239,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -15459,6 +17285,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -15500,6 +17331,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -15541,6 +17377,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -15582,6 +17423,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -15623,6 +17469,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -15664,6 +17515,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -15705,6 +17561,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>gamme halal minoritaire</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -15746,6 +17607,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -15787,6 +17653,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -15828,6 +17699,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -15869,6 +17745,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -15910,6 +17791,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -15951,6 +17837,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -15992,6 +17883,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -16033,6 +17929,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -16074,6 +17975,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -16115,6 +18021,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -16156,6 +18067,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -16197,6 +18113,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -16238,6 +18159,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -16279,6 +18205,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -16320,6 +18251,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -16361,6 +18297,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -16402,6 +18343,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -16443,6 +18389,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -16484,6 +18435,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -16525,6 +18481,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -16566,6 +18527,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -16607,6 +18573,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -16648,6 +18619,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -16689,6 +18665,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -16730,6 +18711,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -16771,6 +18757,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>hors bras halal</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -16812,9 +18803,14 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>specialiste halal</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K399"/>
+  <autoFilter ref="A1:L399"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16825,7 +18821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -16898,17 +18894,38 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>profil        part du catalogue tague halal (sortie D4). Le rang</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ce classement ne dit rien de la halalite ni de la conformite</t>
+          <t xml:space="preserve">              d'un generaliste est fixe par ses produits non halal</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              et ne dit rien de sa gamme halal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ce classement ne dit rien de la halalite ni de la conformite</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>d'aucun produit.</t>
         </is>
